--- a/data/semesters/sem2/courses.xlsx
+++ b/data/semesters/sem2/courses.xlsx
@@ -699,7 +699,11 @@
           <t>CE100-A,CE100-B</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
@@ -764,7 +768,11 @@
           <t>PM100-A</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
@@ -1213,7 +1221,11 @@
           <t>CE100-A,CE100-B</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1465,7 +1477,11 @@
           <t>CE200-A,CE200-B</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
@@ -1528,7 +1544,11 @@
           <t>CE200-A,CE200-B</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
@@ -1654,7 +1674,11 @@
           <t>CE200-A,CE200-B</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
@@ -1717,7 +1741,11 @@
           <t>CE200-A,CE200-B</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
@@ -2032,7 +2060,11 @@
           <t>CE300-A,CE300-B</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
@@ -2099,7 +2131,11 @@
           <t>GM300-A,GM300-B</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
@@ -2166,7 +2202,11 @@
           <t>CE300-A,CE300-B</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
@@ -2292,7 +2332,11 @@
           <t>CE300-A,CE300-B</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
@@ -2544,7 +2588,11 @@
           <t>CE300-A,CE300-B</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
@@ -2796,7 +2844,11 @@
           <t>CE400-A,CE400-B</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
@@ -2926,7 +2978,11 @@
           <t>CE400-A,CE400-B</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
@@ -2989,7 +3045,11 @@
           <t>CE400-A,CE400-B</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
@@ -3052,7 +3112,11 @@
           <t>CE400-A,CE400-B</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
@@ -3505,7 +3569,11 @@
           <t>CV100-A,CV100-B</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
@@ -4332,7 +4400,11 @@
           <t>CV200-A,CV200-B</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
@@ -4521,7 +4593,11 @@
           <t>CV300-A,CV300-B</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
@@ -4773,7 +4849,11 @@
           <t>CV300-A,CV300-B</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
@@ -4962,7 +5042,11 @@
           <t>DS100-A</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr"/>
@@ -5289,7 +5373,11 @@
           <t>DS100-A</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
@@ -5415,7 +5503,11 @@
           <t>DS100-A</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr"/>
@@ -5793,7 +5885,11 @@
           <t>DS200-A</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr"/>
@@ -6431,7 +6527,11 @@
           <t>MF100-A</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr">
         <is>
@@ -6498,7 +6598,11 @@
           <t>EL100-A,EL100-B</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr"/>
@@ -6624,7 +6728,11 @@
           <t>EL100-A,EL100-B</t>
         </is>
       </c>
-      <c r="P97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr"/>
@@ -7132,7 +7240,11 @@
           <t>EL200-A,EL200-B</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr"/>
@@ -7640,7 +7752,11 @@
           <t>EL300-A,EL300-B</t>
         </is>
       </c>
-      <c r="P113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr"/>
@@ -7703,7 +7819,11 @@
           <t>EL300-A,EL300-B</t>
         </is>
       </c>
-      <c r="P114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr"/>
@@ -7892,7 +8012,11 @@
           <t>EL400-A,EL400-B</t>
         </is>
       </c>
-      <c r="P117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr"/>
@@ -7955,7 +8079,11 @@
           <t>EL400-A,EL400-B</t>
         </is>
       </c>
-      <c r="P118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr"/>
@@ -8467,7 +8595,11 @@
           <t>ES100-A,ES100-B</t>
         </is>
       </c>
-      <c r="P126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr"/>
@@ -8593,7 +8725,11 @@
           <t>ES100-A,ES100-B</t>
         </is>
       </c>
-      <c r="P128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr"/>
@@ -8849,7 +8985,11 @@
           <t>ES200-A,ES200-B</t>
         </is>
       </c>
-      <c r="P132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr"/>
@@ -9357,7 +9497,11 @@
           <t>ES300-A,ES300-B</t>
         </is>
       </c>
-      <c r="P140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr">
         <is>
@@ -9424,7 +9568,11 @@
           <t>CV300-A,CV300-B</t>
         </is>
       </c>
-      <c r="P141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr">
         <is>
@@ -9810,7 +9958,11 @@
           <t>ES300-A,ES300-B</t>
         </is>
       </c>
-      <c r="P147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q147" t="inlineStr"/>
       <c r="R147" t="inlineStr"/>
       <c r="S147" t="inlineStr"/>
@@ -10062,7 +10214,11 @@
           <t>ES400-A,ES400-B</t>
         </is>
       </c>
-      <c r="P151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr">
         <is>
@@ -10129,7 +10285,11 @@
           <t>GL400-A,GL400-B</t>
         </is>
       </c>
-      <c r="P152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr">
         <is>
@@ -10196,7 +10356,11 @@
           <t>GM400-A,GM400-B</t>
         </is>
       </c>
-      <c r="P153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q153" t="inlineStr"/>
       <c r="R153" t="inlineStr">
         <is>
@@ -12706,7 +12870,11 @@
           <t>GL400-A,GL400-B</t>
         </is>
       </c>
-      <c r="P191" t="inlineStr"/>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q191" t="inlineStr"/>
       <c r="R191" t="inlineStr"/>
       <c r="S191" t="inlineStr"/>
@@ -15378,7 +15546,11 @@
           <t>MA400-A</t>
         </is>
       </c>
-      <c r="P231" t="inlineStr"/>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q231" t="inlineStr"/>
       <c r="R231" t="inlineStr"/>
       <c r="S231" t="inlineStr"/>
@@ -17261,7 +17433,11 @@
           <t>MC400-A,MC400-B</t>
         </is>
       </c>
-      <c r="P260" t="inlineStr"/>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q260" t="inlineStr"/>
       <c r="R260" t="inlineStr">
         <is>
@@ -17328,7 +17504,11 @@
           <t>MA400-A</t>
         </is>
       </c>
-      <c r="P261" t="inlineStr"/>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q261" t="inlineStr"/>
       <c r="R261" t="inlineStr">
         <is>
@@ -17466,7 +17646,11 @@
           <t>MA400-A</t>
         </is>
       </c>
-      <c r="P263" t="inlineStr"/>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q263" t="inlineStr"/>
       <c r="R263" t="inlineStr">
         <is>
@@ -17533,7 +17717,11 @@
           <t>MC400-A,MC400-B</t>
         </is>
       </c>
-      <c r="P264" t="inlineStr"/>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q264" t="inlineStr"/>
       <c r="R264" t="inlineStr">
         <is>
@@ -17600,7 +17788,11 @@
           <t>EL400-A,EL400-B</t>
         </is>
       </c>
-      <c r="P265" t="inlineStr"/>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q265" t="inlineStr"/>
       <c r="R265" t="inlineStr">
         <is>
@@ -17809,7 +18001,11 @@
           <t>MA400-A</t>
         </is>
       </c>
-      <c r="P268" t="inlineStr"/>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q268" t="inlineStr"/>
       <c r="R268" t="inlineStr">
         <is>
@@ -18258,7 +18454,11 @@
           <t>MF100-A</t>
         </is>
       </c>
-      <c r="P275" t="inlineStr"/>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q275" t="inlineStr"/>
       <c r="R275" t="inlineStr"/>
       <c r="S275" t="inlineStr"/>
@@ -18969,7 +19169,11 @@
           <t>TM100-A</t>
         </is>
       </c>
-      <c r="P286" t="inlineStr"/>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="Q286" t="inlineStr"/>
       <c r="R286" t="inlineStr"/>
       <c r="S286" t="inlineStr"/>

--- a/data/semesters/sem2/courses.xlsx
+++ b/data/semesters/sem2/courses.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S290"/>
+  <dimension ref="A1:Q290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,16 +502,6 @@
           <t>size</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>group_id</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>group_size</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -521,7 +511,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CE 142</t>
+          <t>Basic French II</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -577,8 +567,6 @@
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -588,7 +576,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CE 156</t>
+          <t>Engineering Drawing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -640,8 +628,6 @@
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -651,7 +637,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CE 158/PM 138</t>
+          <t>Academic Writing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -705,12 +691,6 @@
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>joint-5</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -720,7 +700,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CE 158/PM 138</t>
+          <t>Communication Skills II</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -774,12 +754,6 @@
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>joint-5</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -789,7 +763,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CE 162</t>
+          <t>Object-Oriented Programming</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -845,8 +819,6 @@
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -856,7 +828,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CE 162</t>
+          <t>Object-Oriented Programming</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -908,8 +880,6 @@
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -919,7 +889,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CE 164</t>
+          <t>Basic Electronics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -971,8 +941,6 @@
       </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -982,7 +950,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CE 166</t>
+          <t>Calculus</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1034,8 +1002,6 @@
       </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1045,7 +1011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CE 170</t>
+          <t>Database Systems</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1097,8 +1063,6 @@
       </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1108,7 +1072,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CE 170</t>
+          <t>Database Systems</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1160,8 +1124,6 @@
       </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1171,7 +1133,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CE 172</t>
+          <t>Web Programmimg</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1227,8 +1189,6 @@
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1238,7 +1198,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CE 252</t>
+          <t>Engineering Practice</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1290,8 +1250,6 @@
       </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1301,7 +1259,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CE 256</t>
+          <t>Critical Thinking and Integrated Thought</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1353,8 +1311,6 @@
       </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1364,7 +1320,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CE 260</t>
+          <t>Mathematical   Analysis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1416,8 +1372,6 @@
       </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1427,7 +1381,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CE 266</t>
+          <t>Circuit Theory</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1483,8 +1437,6 @@
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1494,7 +1446,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CE 270</t>
+          <t>Microprocessors and Microcontrollers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1550,8 +1502,6 @@
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1561,7 +1511,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CE 270</t>
+          <t>Microprocessors and Microcontrollers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1613,8 +1563,6 @@
       </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1624,7 +1572,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CE 272</t>
+          <t>Signals and Systems</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1680,8 +1628,6 @@
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1691,7 +1637,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CE 276</t>
+          <t>Software Engineering</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1747,8 +1693,6 @@
         </is>
       </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1758,7 +1702,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CE 276</t>
+          <t>Software Engineering</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1810,8 +1754,6 @@
       </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1821,7 +1763,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CE 278</t>
+          <t>Embedded Systems Design</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1873,8 +1815,6 @@
       </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1884,7 +1824,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CE 278</t>
+          <t>Embedded Systems Design</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1936,8 +1876,6 @@
       </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1947,7 +1885,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CE 352</t>
+          <t>Research  Methods and Ethics</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1999,8 +1937,6 @@
       </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2010,7 +1946,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CE 354/GM 354</t>
+          <t>Business Entrepreneurship</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2066,12 +2002,6 @@
         </is>
       </c>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>joint-45</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2081,7 +2011,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CE 354/GM 354</t>
+          <t>Business Entrepreneurship</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2137,12 +2067,6 @@
         </is>
       </c>
       <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>joint-45</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2152,7 +2076,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CE 364</t>
+          <t>Data Science and Machine Learning Fundamentals</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2208,8 +2132,6 @@
         </is>
       </c>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2219,7 +2141,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CE 364</t>
+          <t>Data Science and Machine Learning Fundamentals</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2271,8 +2193,6 @@
       </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2282,7 +2202,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CE 372</t>
+          <t>Information and Cyber Security</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2338,8 +2258,6 @@
         </is>
       </c>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2349,7 +2267,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CE 372</t>
+          <t>Information and Cyber Security</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2401,8 +2319,6 @@
       </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2412,7 +2328,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CE 378</t>
+          <t>Simulation and Modelling</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2464,8 +2380,6 @@
       </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2475,7 +2389,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CE 378</t>
+          <t>Simulation and Modelling</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2527,8 +2441,6 @@
       </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2538,7 +2450,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CE 380</t>
+          <t>Programming with C#</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2594,8 +2506,6 @@
         </is>
       </c>
       <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2605,7 +2515,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CE 382</t>
+          <t>Human Computer Interaction</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2657,8 +2567,6 @@
       </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2668,7 +2576,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CE 384</t>
+          <t>Computer  Lab Work II</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2720,8 +2628,6 @@
       </c>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2731,7 +2637,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CE 384</t>
+          <t>Computer  Lab Work II</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2783,8 +2689,6 @@
       </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2850,8 +2754,6 @@
         </is>
       </c>
       <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2917,8 +2819,6 @@
         </is>
       </c>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2928,7 +2828,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CE 458</t>
+          <t>Organisational Leadership and Management</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2984,8 +2884,6 @@
         </is>
       </c>
       <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2995,7 +2893,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CE 460</t>
+          <t>Corporate Social Responsibility</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3051,8 +2949,6 @@
         </is>
       </c>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3062,7 +2958,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CE 470</t>
+          <t>Compiler Design</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3118,8 +3014,6 @@
         </is>
       </c>
       <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3129,7 +3023,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CE 472</t>
+          <t>Control Systems</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3185,8 +3079,6 @@
         </is>
       </c>
       <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3196,7 +3088,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CE 474</t>
+          <t>Logic of Computer Science</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3252,8 +3144,6 @@
         </is>
       </c>
       <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3263,7 +3153,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CE 474</t>
+          <t>Logic of Computer Science</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3315,8 +3205,6 @@
       </c>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3326,7 +3214,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CV 142</t>
+          <t>Basic French II</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3382,8 +3270,6 @@
         </is>
       </c>
       <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3393,7 +3279,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CV 150</t>
+          <t>Calculus</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3445,8 +3331,6 @@
       </c>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3456,7 +3340,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CV 152</t>
+          <t>Strength of Materials</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3508,8 +3392,6 @@
       </c>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3519,7 +3401,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CV 158</t>
+          <t>Academic Writing</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3575,8 +3457,6 @@
         </is>
       </c>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3586,7 +3466,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CV 162</t>
+          <t>Applied Electronics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3638,8 +3518,6 @@
       </c>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3705,8 +3583,6 @@
         </is>
       </c>
       <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3716,7 +3592,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CV 172</t>
+          <t>Properties of Civil Engineering Materials</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3768,8 +3644,6 @@
       </c>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3779,7 +3653,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CV 174</t>
+          <t>Elementary Structures</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3831,8 +3705,6 @@
       </c>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3842,7 +3714,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CV 176</t>
+          <t>Civil Engineering Drawing</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3894,8 +3766,6 @@
       </c>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3905,7 +3775,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CV 250</t>
+          <t>Mathematical Analysis</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3961,8 +3831,6 @@
         </is>
       </c>
       <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3972,7 +3840,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CV 252</t>
+          <t>Engineering Practice</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4024,8 +3892,6 @@
       </c>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4035,7 +3901,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CV 254</t>
+          <t>Soil Mechanics I</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4087,8 +3953,6 @@
       </c>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4098,7 +3962,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CV 254</t>
+          <t>Soil Mechanics I</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4150,8 +4014,6 @@
       </c>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4161,7 +4023,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CV 264</t>
+          <t>Fluid Mechanics</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4213,8 +4075,6 @@
       </c>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4224,7 +4084,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CV 270</t>
+          <t>Structural Analysis</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4276,8 +4136,6 @@
       </c>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4287,7 +4145,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CV 272</t>
+          <t>Engineering Survey</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4339,8 +4197,6 @@
       </c>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4350,7 +4206,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CV 274</t>
+          <t>Introduction to Environmental Engineering and Management</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4406,8 +4262,6 @@
         </is>
       </c>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4417,7 +4271,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CV 352</t>
+          <t>Research Methods and Ethics</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4469,8 +4323,6 @@
       </c>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4480,7 +4332,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CV 356</t>
+          <t>Fieldtrip and Technical Report Writing</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4532,8 +4384,6 @@
       </c>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4543,7 +4393,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CV 370</t>
+          <t>Engineering Economics and Project Management</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4599,8 +4449,6 @@
         </is>
       </c>
       <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4610,7 +4458,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CV 372</t>
+          <t>Foundation Engineering</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4662,8 +4510,6 @@
       </c>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4673,7 +4519,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CV 374</t>
+          <t>Steel and Timber Design</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4725,8 +4571,6 @@
       </c>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4736,7 +4580,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CV 376</t>
+          <t>Civil Engineering Quantities</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4788,8 +4632,6 @@
       </c>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4799,7 +4641,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CV 378</t>
+          <t>Hydraulic Engineering</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4855,8 +4697,6 @@
         </is>
       </c>
       <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4866,7 +4706,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CV 380</t>
+          <t>Transportation Planning</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4918,8 +4758,6 @@
       </c>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4929,7 +4767,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DS 146</t>
+          <t>Programming with R</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4981,8 +4819,6 @@
       </c>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4992,7 +4828,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DS 156</t>
+          <t>Fundamentals of Big Data</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5048,8 +4884,6 @@
         </is>
       </c>
       <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5059,7 +4893,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DS 156</t>
+          <t>Fundamentals of Big Data</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5111,8 +4945,6 @@
       </c>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5122,7 +4954,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DS 158/TM 158</t>
+          <t>Academic Writing</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5174,14 +5006,6 @@
       </c>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>joint-128</t>
-        </is>
-      </c>
-      <c r="S73" t="n">
-        <v>69</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5191,7 +5015,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DS 158/TM 158</t>
+          <t>Academic Writing</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5243,14 +5067,6 @@
       </c>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>joint-128</t>
-        </is>
-      </c>
-      <c r="S74" t="n">
-        <v>69</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5260,7 +5076,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DS 166</t>
+          <t>Calculus</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5312,8 +5128,6 @@
       </c>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5323,7 +5137,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DS 170</t>
+          <t>Database Systems</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5379,8 +5193,6 @@
         </is>
       </c>
       <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5390,7 +5202,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DS 170</t>
+          <t>Database Systems</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5442,8 +5254,6 @@
       </c>
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5453,7 +5263,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DS 172</t>
+          <t>Web Programming</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5509,8 +5319,6 @@
         </is>
       </c>
       <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5520,7 +5328,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DS 174</t>
+          <t>Systems Analysis and Design</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5572,8 +5380,6 @@
       </c>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5635,8 +5441,6 @@
       </c>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5646,7 +5450,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DS 252</t>
+          <t>Information Retrieval</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5698,8 +5502,6 @@
       </c>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5709,7 +5511,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DS 256</t>
+          <t>Critical Thinking and Integrated Though</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5761,8 +5563,6 @@
       </c>
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5772,7 +5572,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DS 260</t>
+          <t>Mathematical Analysis</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5824,8 +5624,6 @@
       </c>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5835,7 +5633,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DS 266</t>
+          <t>Big Data Management</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5891,8 +5689,6 @@
         </is>
       </c>
       <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5902,7 +5698,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DS 270</t>
+          <t>Time Series and Regression Analysis</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5954,8 +5750,6 @@
       </c>
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5965,7 +5759,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DS 272</t>
+          <t>Predictive and Descriptive Analytical with R</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6017,8 +5811,6 @@
       </c>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6028,7 +5820,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>DS 276</t>
+          <t>Software Engineering</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6080,8 +5872,6 @@
       </c>
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6091,7 +5881,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>DS 278</t>
+          <t>Machine Learning: Principles and Tecniques</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6143,8 +5933,6 @@
       </c>
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6154,7 +5942,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DS 278</t>
+          <t>Machine Learning: Principles and Tecniques</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6206,8 +5994,6 @@
       </c>
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6217,7 +6003,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EL 142</t>
+          <t>Basic French II</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6273,8 +6059,6 @@
         </is>
       </c>
       <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6284,7 +6068,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EL 152</t>
+          <t>Strenght of Materials</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6336,8 +6120,6 @@
       </c>
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6347,7 +6129,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EL 156</t>
+          <t>Engineering Drawing</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6399,8 +6181,6 @@
       </c>
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6410,7 +6190,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EL 158</t>
+          <t>Academic Writing</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6466,8 +6246,6 @@
         </is>
       </c>
       <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6477,7 +6255,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EL 158/MF 158</t>
+          <t>Academic Writing</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6533,12 +6311,6 @@
         </is>
       </c>
       <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr">
-        <is>
-          <t>joint-160</t>
-        </is>
-      </c>
-      <c r="S94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6548,7 +6320,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EL 162</t>
+          <t>Object -Oriented Programming</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6604,8 +6376,6 @@
         </is>
       </c>
       <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6615,7 +6385,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EL 162</t>
+          <t>Object -Oriented Programming</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6667,8 +6437,6 @@
       </c>
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6678,7 +6446,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EL 164</t>
+          <t>Basic Electronics</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6734,8 +6502,6 @@
         </is>
       </c>
       <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6745,7 +6511,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EL 166</t>
+          <t>Calculus</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6797,8 +6563,6 @@
       </c>
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6808,7 +6572,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EL 168</t>
+          <t>Basic Material Science</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6860,8 +6624,6 @@
       </c>
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6871,7 +6633,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>EL 172</t>
+          <t>Instruments and Measurements</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6927,8 +6689,6 @@
         </is>
       </c>
       <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="inlineStr"/>
-      <c r="S100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6938,7 +6698,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>EL 252</t>
+          <t>Engineering  Practice</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6990,8 +6750,6 @@
       </c>
       <c r="P101" t="inlineStr"/>
       <c r="Q101" t="inlineStr"/>
-      <c r="R101" t="inlineStr"/>
-      <c r="S101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7001,7 +6759,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>EL 256</t>
+          <t>Critical Thinking and Intergrated Thought</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7053,8 +6811,6 @@
       </c>
       <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr"/>
-      <c r="R102" t="inlineStr"/>
-      <c r="S102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7064,7 +6820,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>EL 260</t>
+          <t>Mathematical Analysis</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7116,8 +6872,6 @@
       </c>
       <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr"/>
-      <c r="R103" t="inlineStr"/>
-      <c r="S103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7127,7 +6881,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>EL 264</t>
+          <t>Fluid  Machanics</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7179,8 +6933,6 @@
       </c>
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
-      <c r="R104" t="inlineStr"/>
-      <c r="S104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7190,7 +6942,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>EL 266</t>
+          <t>Circuit Theory</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7246,8 +6998,6 @@
         </is>
       </c>
       <c r="Q105" t="inlineStr"/>
-      <c r="R105" t="inlineStr"/>
-      <c r="S105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7257,7 +7007,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>EL 270</t>
+          <t>Digital Electronics</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7313,8 +7063,6 @@
         </is>
       </c>
       <c r="Q106" t="inlineStr"/>
-      <c r="R106" t="inlineStr"/>
-      <c r="S106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7324,7 +7072,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>EL 272</t>
+          <t>Industrial Electronics</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7376,8 +7124,6 @@
       </c>
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
-      <c r="R107" t="inlineStr"/>
-      <c r="S107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7387,7 +7133,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>EL 274</t>
+          <t>Electromagnetic Field Theory</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7439,8 +7185,6 @@
       </c>
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
-      <c r="R108" t="inlineStr"/>
-      <c r="S108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7450,7 +7194,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>EL 352</t>
+          <t>Research Method and Ethics</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7502,8 +7246,6 @@
       </c>
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
-      <c r="R109" t="inlineStr"/>
-      <c r="S109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7513,7 +7255,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EL 356</t>
+          <t>Fieldtrip and Technical Report Writing</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7565,8 +7307,6 @@
       </c>
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="inlineStr"/>
-      <c r="S110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7576,7 +7316,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EL 364</t>
+          <t>Data Science and Machine Learning Fundamentals</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7628,8 +7368,6 @@
       </c>
       <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr"/>
-      <c r="R111" t="inlineStr"/>
-      <c r="S111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7639,7 +7377,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>EL 372</t>
+          <t>Utilisation of Electrical Power</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7691,8 +7429,6 @@
       </c>
       <c r="P112" t="inlineStr"/>
       <c r="Q112" t="inlineStr"/>
-      <c r="R112" t="inlineStr"/>
-      <c r="S112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7702,7 +7438,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>EL 374</t>
+          <t>Signals and System</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7758,8 +7494,6 @@
         </is>
       </c>
       <c r="Q113" t="inlineStr"/>
-      <c r="R113" t="inlineStr"/>
-      <c r="S113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7769,7 +7503,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EL 376</t>
+          <t>Basic Communication Sysytems</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7825,8 +7559,6 @@
         </is>
       </c>
       <c r="Q114" t="inlineStr"/>
-      <c r="R114" t="inlineStr"/>
-      <c r="S114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7836,7 +7568,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>EL 382</t>
+          <t>Microprocessors and Digital Systems</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7888,8 +7620,6 @@
       </c>
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr"/>
-      <c r="R115" t="inlineStr"/>
-      <c r="S115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7951,8 +7681,6 @@
       </c>
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr"/>
-      <c r="R116" t="inlineStr"/>
-      <c r="S116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7962,7 +7690,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>EL 458</t>
+          <t>Organisational Leadership and Management</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -8018,8 +7746,6 @@
         </is>
       </c>
       <c r="Q117" t="inlineStr"/>
-      <c r="R117" t="inlineStr"/>
-      <c r="S117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8029,7 +7755,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>EL 460</t>
+          <t>Corporate Social Responsibility</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -8085,8 +7811,6 @@
         </is>
       </c>
       <c r="Q118" t="inlineStr"/>
-      <c r="R118" t="inlineStr"/>
-      <c r="S118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8096,7 +7820,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EL 472</t>
+          <t>Electric Haulage Machinery</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -8148,8 +7872,6 @@
       </c>
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr"/>
-      <c r="R119" t="inlineStr"/>
-      <c r="S119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8159,7 +7881,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EL 474</t>
+          <t>Electrical Drive Systems</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -8211,8 +7933,6 @@
       </c>
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr"/>
-      <c r="R120" t="inlineStr"/>
-      <c r="S120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8222,7 +7942,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ES 142</t>
+          <t>Basic French II</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8278,8 +7998,6 @@
         </is>
       </c>
       <c r="Q121" t="inlineStr"/>
-      <c r="R121" t="inlineStr"/>
-      <c r="S121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8289,7 +8007,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ES 150</t>
+          <t>Calculus</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -8341,8 +8059,6 @@
       </c>
       <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr"/>
-      <c r="R122" t="inlineStr"/>
-      <c r="S122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8352,7 +8068,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ES 152</t>
+          <t>Strength of Materials</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8404,8 +8120,6 @@
       </c>
       <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr"/>
-      <c r="R123" t="inlineStr"/>
-      <c r="S123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8415,7 +8129,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ES 156</t>
+          <t>Engineering Drawing</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8467,8 +8181,6 @@
       </c>
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
-      <c r="R124" t="inlineStr"/>
-      <c r="S124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8478,7 +8190,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ES 158</t>
+          <t>Academic Writing</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8534,8 +8246,6 @@
         </is>
       </c>
       <c r="Q125" t="inlineStr"/>
-      <c r="R125" t="inlineStr"/>
-      <c r="S125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8545,7 +8255,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ES 160</t>
+          <t>Mineralogy &amp; Petrology</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8601,8 +8311,6 @@
         </is>
       </c>
       <c r="Q126" t="inlineStr"/>
-      <c r="R126" t="inlineStr"/>
-      <c r="S126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8612,7 +8320,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ES 162</t>
+          <t>Applied Electronics</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8664,8 +8372,6 @@
       </c>
       <c r="P127" t="inlineStr"/>
       <c r="Q127" t="inlineStr"/>
-      <c r="R127" t="inlineStr"/>
-      <c r="S127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8675,7 +8381,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ES 170</t>
+          <t>Chemistry for  Environmental Engineers</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8731,8 +8437,6 @@
         </is>
       </c>
       <c r="Q128" t="inlineStr"/>
-      <c r="R128" t="inlineStr"/>
-      <c r="S128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8742,7 +8446,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ES 172</t>
+          <t>Introdution to Safety Management</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8794,8 +8498,6 @@
       </c>
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
-      <c r="R129" t="inlineStr"/>
-      <c r="S129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8805,7 +8507,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ES 172</t>
+          <t>Introdution to Safety Management</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8861,8 +8563,6 @@
         </is>
       </c>
       <c r="Q130" t="inlineStr"/>
-      <c r="R130" t="inlineStr"/>
-      <c r="S130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8872,7 +8572,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ES 250</t>
+          <t>Mathematical Analysis</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8924,8 +8624,6 @@
       </c>
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
-      <c r="R131" t="inlineStr"/>
-      <c r="S131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8935,7 +8633,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ES 256</t>
+          <t>Critical Thinking and Integrated Thought</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8991,8 +8689,6 @@
         </is>
       </c>
       <c r="Q132" t="inlineStr"/>
-      <c r="R132" t="inlineStr"/>
-      <c r="S132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -9002,7 +8698,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ES 264</t>
+          <t>Fluid  Mechanics</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -9054,8 +8750,6 @@
       </c>
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
-      <c r="R133" t="inlineStr"/>
-      <c r="S133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9065,7 +8759,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ES 266</t>
+          <t>Basics of Mining and Mineral Processing</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -9121,8 +8815,6 @@
         </is>
       </c>
       <c r="Q134" t="inlineStr"/>
-      <c r="R134" t="inlineStr"/>
-      <c r="S134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9132,7 +8824,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ES 272</t>
+          <t>Elements of Geospatial Science</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -9184,8 +8876,6 @@
       </c>
       <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr"/>
-      <c r="R135" t="inlineStr"/>
-      <c r="S135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9195,7 +8885,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ES 274</t>
+          <t>Environmental Chemistry and Microbiology</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9247,8 +8937,6 @@
       </c>
       <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
-      <c r="R136" t="inlineStr"/>
-      <c r="S136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9258,7 +8946,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ES 276</t>
+          <t>Introduction to Occupational Health</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9310,8 +8998,6 @@
       </c>
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
-      <c r="R137" t="inlineStr"/>
-      <c r="S137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9321,7 +9007,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ES 278</t>
+          <t>Environmental Process Engineering</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9373,8 +9059,6 @@
       </c>
       <c r="P138" t="inlineStr"/>
       <c r="Q138" t="inlineStr"/>
-      <c r="R138" t="inlineStr"/>
-      <c r="S138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -9384,7 +9068,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ES 352</t>
+          <t>Research Methods and Ethics</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9436,8 +9120,6 @@
       </c>
       <c r="P139" t="inlineStr"/>
       <c r="Q139" t="inlineStr"/>
-      <c r="R139" t="inlineStr"/>
-      <c r="S139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -9447,7 +9129,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CV 354/ES 354</t>
+          <t>Business Entrepreneurship</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9503,12 +9185,6 @@
         </is>
       </c>
       <c r="Q140" t="inlineStr"/>
-      <c r="R140" t="inlineStr">
-        <is>
-          <t>joint-271</t>
-        </is>
-      </c>
-      <c r="S140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9518,7 +9194,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>CV 354/ES 354</t>
+          <t>Business Entrepreneurship</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9574,12 +9250,6 @@
         </is>
       </c>
       <c r="Q141" t="inlineStr"/>
-      <c r="R141" t="inlineStr">
-        <is>
-          <t>joint-271</t>
-        </is>
-      </c>
-      <c r="S141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -9589,7 +9259,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ES 356</t>
+          <t>Fieldtrip and Technical Report Writing</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9641,8 +9311,6 @@
       </c>
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr"/>
-      <c r="R142" t="inlineStr"/>
-      <c r="S142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -9652,7 +9320,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ES 370</t>
+          <t>Computer Applications in Environmental  and Safety Eng.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9708,8 +9376,6 @@
         </is>
       </c>
       <c r="Q143" t="inlineStr"/>
-      <c r="R143" t="inlineStr"/>
-      <c r="S143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -9719,7 +9385,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ES 372</t>
+          <t>Hydrology</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9771,8 +9437,6 @@
       </c>
       <c r="P144" t="inlineStr"/>
       <c r="Q144" t="inlineStr"/>
-      <c r="R144" t="inlineStr"/>
-      <c r="S144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9782,7 +9446,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ES 374</t>
+          <t>Hazardous Waste Engineering</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9834,8 +9498,6 @@
       </c>
       <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr"/>
-      <c r="R145" t="inlineStr"/>
-      <c r="S145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9845,7 +9507,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ES 376</t>
+          <t>Safety Technology</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9897,8 +9559,6 @@
       </c>
       <c r="P146" t="inlineStr"/>
       <c r="Q146" t="inlineStr"/>
-      <c r="R146" t="inlineStr"/>
-      <c r="S146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9908,7 +9568,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ES 376</t>
+          <t>Safety Technology</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9964,8 +9624,6 @@
         </is>
       </c>
       <c r="Q147" t="inlineStr"/>
-      <c r="R147" t="inlineStr"/>
-      <c r="S147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9975,7 +9633,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ES 378</t>
+          <t>Water and Wastewater Engineering</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -10027,8 +9685,6 @@
       </c>
       <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr"/>
-      <c r="R148" t="inlineStr"/>
-      <c r="S148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10038,7 +9694,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ES 380</t>
+          <t>Artificial Intelligence in Engineering</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -10090,8 +9746,6 @@
       </c>
       <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr"/>
-      <c r="R149" t="inlineStr"/>
-      <c r="S149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10153,8 +9807,6 @@
       </c>
       <c r="P150" t="inlineStr"/>
       <c r="Q150" t="inlineStr"/>
-      <c r="R150" t="inlineStr"/>
-      <c r="S150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -10164,7 +9816,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ES 460/GL 460/GM 460</t>
+          <t>Corporate Social Responsibility</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -10220,12 +9872,6 @@
         </is>
       </c>
       <c r="Q151" t="inlineStr"/>
-      <c r="R151" t="inlineStr">
-        <is>
-          <t>joint-288</t>
-        </is>
-      </c>
-      <c r="S151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -10235,7 +9881,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ES 460/GL 460/GM 460</t>
+          <t>Corporate Social Responsibility</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -10291,12 +9937,6 @@
         </is>
       </c>
       <c r="Q152" t="inlineStr"/>
-      <c r="R152" t="inlineStr">
-        <is>
-          <t>joint-288</t>
-        </is>
-      </c>
-      <c r="S152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -10306,7 +9946,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ES 460/GL 460/GM 460</t>
+          <t>Corporate Social Responsibility</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -10362,12 +10002,6 @@
         </is>
       </c>
       <c r="Q153" t="inlineStr"/>
-      <c r="R153" t="inlineStr">
-        <is>
-          <t>joint-288</t>
-        </is>
-      </c>
-      <c r="S153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -10377,7 +10011,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ES 470</t>
+          <t>Environmental Design and Urban Drainage</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -10429,8 +10063,6 @@
       </c>
       <c r="P154" t="inlineStr"/>
       <c r="Q154" t="inlineStr"/>
-      <c r="R154" t="inlineStr"/>
-      <c r="S154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -10440,7 +10072,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ES 472</t>
+          <t>Disaster Management and Emergency Preparedness</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -10496,8 +10128,6 @@
         </is>
       </c>
       <c r="Q155" t="inlineStr"/>
-      <c r="R155" t="inlineStr"/>
-      <c r="S155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -10507,7 +10137,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ES 474</t>
+          <t>Environment, Safety, Labour and Compensation Laws</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -10563,8 +10193,6 @@
         </is>
       </c>
       <c r="Q156" t="inlineStr"/>
-      <c r="R156" t="inlineStr"/>
-      <c r="S156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -10574,7 +10202,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>GL 142</t>
+          <t>Basic French II</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10630,8 +10258,6 @@
         </is>
       </c>
       <c r="Q157" t="inlineStr"/>
-      <c r="R157" t="inlineStr"/>
-      <c r="S157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -10641,7 +10267,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>GL 150</t>
+          <t>Calculus</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10697,8 +10323,6 @@
         </is>
       </c>
       <c r="Q158" t="inlineStr"/>
-      <c r="R158" t="inlineStr"/>
-      <c r="S158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -10708,7 +10332,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>GL 152</t>
+          <t>Strength of Materials</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10760,8 +10384,6 @@
       </c>
       <c r="P159" t="inlineStr"/>
       <c r="Q159" t="inlineStr"/>
-      <c r="R159" t="inlineStr"/>
-      <c r="S159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -10771,7 +10393,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>GL 154</t>
+          <t>Physical and Analytical Chemistry</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10827,8 +10449,6 @@
         </is>
       </c>
       <c r="Q160" t="inlineStr"/>
-      <c r="R160" t="inlineStr"/>
-      <c r="S160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -10838,7 +10458,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>GL 156</t>
+          <t>Engineering Drawing</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10894,8 +10514,6 @@
         </is>
       </c>
       <c r="Q161" t="inlineStr"/>
-      <c r="R161" t="inlineStr"/>
-      <c r="S161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -10905,7 +10523,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>GL 158</t>
+          <t>Academic Writing</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10961,8 +10579,6 @@
         </is>
       </c>
       <c r="Q162" t="inlineStr"/>
-      <c r="R162" t="inlineStr"/>
-      <c r="S162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -10972,7 +10588,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>GL 162</t>
+          <t>Applied Electronics</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -11028,8 +10644,6 @@
         </is>
       </c>
       <c r="Q163" t="inlineStr"/>
-      <c r="R163" t="inlineStr"/>
-      <c r="S163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -11039,7 +10653,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>GL 170</t>
+          <t>Crystallography and Mineralogy</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -11091,8 +10705,6 @@
       </c>
       <c r="P164" t="inlineStr"/>
       <c r="Q164" t="inlineStr"/>
-      <c r="R164" t="inlineStr"/>
-      <c r="S164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11102,7 +10714,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>GL 174</t>
+          <t>Principles of Metallurgical Engineering</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -11158,8 +10770,6 @@
         </is>
       </c>
       <c r="Q165" t="inlineStr"/>
-      <c r="R165" t="inlineStr"/>
-      <c r="S165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -11169,7 +10779,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>GL 250</t>
+          <t>Mathematical Analysis</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -11221,8 +10831,6 @@
       </c>
       <c r="P166" t="inlineStr"/>
       <c r="Q166" t="inlineStr"/>
-      <c r="R166" t="inlineStr"/>
-      <c r="S166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -11232,7 +10840,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>GL 252</t>
+          <t>Engineering Practice</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -11284,8 +10892,6 @@
       </c>
       <c r="P167" t="inlineStr"/>
       <c r="Q167" t="inlineStr"/>
-      <c r="R167" t="inlineStr"/>
-      <c r="S167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -11295,7 +10901,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>GL 254</t>
+          <t>Soil Mechanics*</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -11347,8 +10953,6 @@
       </c>
       <c r="P168" t="inlineStr"/>
       <c r="Q168" t="inlineStr"/>
-      <c r="R168" t="inlineStr"/>
-      <c r="S168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -11358,7 +10962,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>GL 254</t>
+          <t>Soil Mechanics*</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -11414,8 +11018,6 @@
         </is>
       </c>
       <c r="Q169" t="inlineStr"/>
-      <c r="R169" t="inlineStr"/>
-      <c r="S169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -11425,7 +11027,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>GL 262</t>
+          <t>Land Surveying*</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -11477,8 +11079,6 @@
       </c>
       <c r="P170" t="inlineStr"/>
       <c r="Q170" t="inlineStr"/>
-      <c r="R170" t="inlineStr"/>
-      <c r="S170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -11488,7 +11088,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>GL 264</t>
+          <t>Fluid  Mechanics</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -11540,8 +11140,6 @@
       </c>
       <c r="P171" t="inlineStr"/>
       <c r="Q171" t="inlineStr"/>
-      <c r="R171" t="inlineStr"/>
-      <c r="S171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -11551,7 +11149,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>GL 272</t>
+          <t>Igneous and Metamorphic Petrology</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -11607,8 +11205,6 @@
         </is>
       </c>
       <c r="Q172" t="inlineStr"/>
-      <c r="R172" t="inlineStr"/>
-      <c r="S172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -11618,7 +11214,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>GL 274</t>
+          <t>Principles of Field Mapping**</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11674,8 +11270,6 @@
         </is>
       </c>
       <c r="Q173" t="inlineStr"/>
-      <c r="R173" t="inlineStr"/>
-      <c r="S173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -11685,7 +11279,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>GL 274</t>
+          <t>Principles of Field Mapping**</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11741,8 +11335,6 @@
         </is>
       </c>
       <c r="Q174" t="inlineStr"/>
-      <c r="R174" t="inlineStr"/>
-      <c r="S174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -11752,7 +11344,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>GL 276</t>
+          <t>Artificial Intelligence in Geological Engineering</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11804,8 +11396,6 @@
       </c>
       <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr"/>
-      <c r="R175" t="inlineStr"/>
-      <c r="S175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -11815,7 +11405,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>GL 350</t>
+          <t>Mineral Resource Estimation</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11867,8 +11457,6 @@
       </c>
       <c r="P176" t="inlineStr"/>
       <c r="Q176" t="inlineStr"/>
-      <c r="R176" t="inlineStr"/>
-      <c r="S176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -11878,7 +11466,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>GL 352</t>
+          <t>Research Methods and Ethics</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11934,8 +11522,6 @@
         </is>
       </c>
       <c r="Q177" t="inlineStr"/>
-      <c r="R177" t="inlineStr"/>
-      <c r="S177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -11945,7 +11531,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>GL 354</t>
+          <t>Business Entrepreneurship</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -12001,8 +11587,6 @@
         </is>
       </c>
       <c r="Q178" t="inlineStr"/>
-      <c r="R178" t="inlineStr"/>
-      <c r="S178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -12012,7 +11596,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>GL 356</t>
+          <t>Fieldtrip and Tech. Report Writing **</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -12064,8 +11648,6 @@
       </c>
       <c r="P179" t="inlineStr"/>
       <c r="Q179" t="inlineStr"/>
-      <c r="R179" t="inlineStr"/>
-      <c r="S179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -12075,7 +11657,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>GL 358</t>
+          <t>Ore Mineralogy &amp; Microscopy*</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -12131,8 +11713,6 @@
         </is>
       </c>
       <c r="Q180" t="inlineStr"/>
-      <c r="R180" t="inlineStr"/>
-      <c r="S180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -12142,7 +11722,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>GL 370</t>
+          <t>Computer Applications in Geology</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -12198,8 +11778,6 @@
         </is>
       </c>
       <c r="Q181" t="inlineStr"/>
-      <c r="R181" t="inlineStr"/>
-      <c r="S181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -12209,7 +11787,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>GL 374</t>
+          <t>Exploration Geochemistry</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -12265,8 +11843,6 @@
         </is>
       </c>
       <c r="Q182" t="inlineStr"/>
-      <c r="R182" t="inlineStr"/>
-      <c r="S182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -12276,7 +11852,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>GL 376</t>
+          <t>Groundwater Geochemistry</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -12332,8 +11908,6 @@
         </is>
       </c>
       <c r="Q183" t="inlineStr"/>
-      <c r="R183" t="inlineStr"/>
-      <c r="S183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -12343,7 +11917,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>GL 376</t>
+          <t>Groundwater Geochemistry</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -12399,8 +11973,6 @@
         </is>
       </c>
       <c r="Q184" t="inlineStr"/>
-      <c r="R184" t="inlineStr"/>
-      <c r="S184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -12410,7 +11982,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>GL 378</t>
+          <t>Exploration Geophysics</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -12466,8 +12038,6 @@
         </is>
       </c>
       <c r="Q185" t="inlineStr"/>
-      <c r="R185" t="inlineStr"/>
-      <c r="S185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -12533,8 +12103,6 @@
         </is>
       </c>
       <c r="Q186" t="inlineStr"/>
-      <c r="R186" t="inlineStr"/>
-      <c r="S186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -12544,7 +12112,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>GL 458</t>
+          <t>Organisational Leadership and Management</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -12600,8 +12168,6 @@
         </is>
       </c>
       <c r="Q187" t="inlineStr"/>
-      <c r="R187" t="inlineStr"/>
-      <c r="S187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -12611,7 +12177,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>CE 466/GL 466</t>
+          <t>Law of Contract and Tort</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -12667,12 +12233,6 @@
         </is>
       </c>
       <c r="Q188" t="inlineStr"/>
-      <c r="R188" t="inlineStr">
-        <is>
-          <t>joint-353</t>
-        </is>
-      </c>
-      <c r="S188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -12682,7 +12242,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>CE 466/GL 466</t>
+          <t>Law of Contract and Tort</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -12738,12 +12298,6 @@
         </is>
       </c>
       <c r="Q189" t="inlineStr"/>
-      <c r="R189" t="inlineStr">
-        <is>
-          <t>joint-353</t>
-        </is>
-      </c>
-      <c r="S189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -12753,7 +12307,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>GL 472</t>
+          <t>Foundation Engineering**</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12809,8 +12363,6 @@
         </is>
       </c>
       <c r="Q190" t="inlineStr"/>
-      <c r="R190" t="inlineStr"/>
-      <c r="S190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -12820,7 +12372,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>GL 474</t>
+          <t>Applied Geotechnics**</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12876,8 +12428,6 @@
         </is>
       </c>
       <c r="Q191" t="inlineStr"/>
-      <c r="R191" t="inlineStr"/>
-      <c r="S191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -12887,7 +12437,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>GL 476</t>
+          <t>Environmental Geology</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12943,8 +12493,6 @@
         </is>
       </c>
       <c r="Q192" t="inlineStr"/>
-      <c r="R192" t="inlineStr"/>
-      <c r="S192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -12954,7 +12502,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>GL 476</t>
+          <t>Environmental Geology</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -13010,8 +12558,6 @@
         </is>
       </c>
       <c r="Q193" t="inlineStr"/>
-      <c r="R193" t="inlineStr"/>
-      <c r="S193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -13021,7 +12567,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>GM 142</t>
+          <t>Basic French II</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -13077,8 +12623,6 @@
         </is>
       </c>
       <c r="Q194" t="inlineStr"/>
-      <c r="R194" t="inlineStr"/>
-      <c r="S194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -13088,7 +12632,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>GM 150</t>
+          <t>Calculus</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -13144,8 +12688,6 @@
         </is>
       </c>
       <c r="Q195" t="inlineStr"/>
-      <c r="R195" t="inlineStr"/>
-      <c r="S195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -13155,7 +12697,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>GM 156</t>
+          <t>Engineering Drawing</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -13211,8 +12753,6 @@
         </is>
       </c>
       <c r="Q196" t="inlineStr"/>
-      <c r="R196" t="inlineStr"/>
-      <c r="S196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -13222,7 +12762,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>GM 158</t>
+          <t>Academic Writing</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -13278,8 +12818,6 @@
         </is>
       </c>
       <c r="Q197" t="inlineStr"/>
-      <c r="R197" t="inlineStr"/>
-      <c r="S197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -13289,7 +12827,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>GM 162</t>
+          <t>Applied Electronics</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -13345,8 +12883,6 @@
         </is>
       </c>
       <c r="Q198" t="inlineStr"/>
-      <c r="R198" t="inlineStr"/>
-      <c r="S198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -13356,7 +12892,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>GM 170</t>
+          <t>Survey Measurements</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -13408,8 +12944,6 @@
       </c>
       <c r="P199" t="inlineStr"/>
       <c r="Q199" t="inlineStr"/>
-      <c r="R199" t="inlineStr"/>
-      <c r="S199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -13419,7 +12953,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>GM 172</t>
+          <t>Applied Optics and Signal Processing</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -13475,8 +13009,6 @@
         </is>
       </c>
       <c r="Q200" t="inlineStr"/>
-      <c r="R200" t="inlineStr"/>
-      <c r="S200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -13486,7 +13018,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>GM 174</t>
+          <t>Solid Geometry</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -13538,8 +13070,6 @@
       </c>
       <c r="P201" t="inlineStr"/>
       <c r="Q201" t="inlineStr"/>
-      <c r="R201" t="inlineStr"/>
-      <c r="S201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -13549,7 +13079,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>GM 250</t>
+          <t>Mathematical Analysis</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -13605,8 +13135,6 @@
         </is>
       </c>
       <c r="Q202" t="inlineStr"/>
-      <c r="R202" t="inlineStr"/>
-      <c r="S202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -13616,7 +13144,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>GM 252</t>
+          <t>Engineering Practice</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -13668,8 +13196,6 @@
       </c>
       <c r="P203" t="inlineStr"/>
       <c r="Q203" t="inlineStr"/>
-      <c r="R203" t="inlineStr"/>
-      <c r="S203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -13679,7 +13205,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>CV 256/GL 256/GM 256</t>
+          <t>Critical Thinking &amp; Integrated Thought</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -13735,12 +13261,6 @@
         </is>
       </c>
       <c r="Q204" t="inlineStr"/>
-      <c r="R204" t="inlineStr">
-        <is>
-          <t>joint-388</t>
-        </is>
-      </c>
-      <c r="S204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -13750,7 +13270,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>CV 256/GL 256/GM 256</t>
+          <t>Critical Thinking and Integrated Thought</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -13806,12 +13326,6 @@
         </is>
       </c>
       <c r="Q205" t="inlineStr"/>
-      <c r="R205" t="inlineStr">
-        <is>
-          <t>joint-388</t>
-        </is>
-      </c>
-      <c r="S205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -13821,7 +13335,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>CV 256/GL 256/GM 256</t>
+          <t>Critical Thinking &amp; Intergrated Thought</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13877,12 +13391,6 @@
         </is>
       </c>
       <c r="Q206" t="inlineStr"/>
-      <c r="R206" t="inlineStr">
-        <is>
-          <t>joint-388</t>
-        </is>
-      </c>
-      <c r="S206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -13892,7 +13400,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>GM 272</t>
+          <t>Advanced Photogrammetry</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13944,8 +13452,6 @@
       </c>
       <c r="P207" t="inlineStr"/>
       <c r="Q207" t="inlineStr"/>
-      <c r="R207" t="inlineStr"/>
-      <c r="S207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -13955,7 +13461,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>GM 274</t>
+          <t>Survey Computation &amp; Adjustment  I</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -14011,8 +13517,6 @@
         </is>
       </c>
       <c r="Q208" t="inlineStr"/>
-      <c r="R208" t="inlineStr"/>
-      <c r="S208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -14022,7 +13526,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>GM 276</t>
+          <t>Principles of Remote Sensing and Drone Technology</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -14078,8 +13582,6 @@
         </is>
       </c>
       <c r="Q209" t="inlineStr"/>
-      <c r="R209" t="inlineStr"/>
-      <c r="S209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -14089,7 +13591,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>GM 278</t>
+          <t>Mine Surveying II</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -14145,8 +13647,6 @@
         </is>
       </c>
       <c r="Q210" t="inlineStr"/>
-      <c r="R210" t="inlineStr"/>
-      <c r="S210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -14156,7 +13656,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>GM 280</t>
+          <t>Survey Camp I **</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -14212,8 +13712,6 @@
         </is>
       </c>
       <c r="Q211" t="inlineStr"/>
-      <c r="R211" t="inlineStr"/>
-      <c r="S211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -14223,7 +13721,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>GM 280</t>
+          <t>Survey Camp I **</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -14279,8 +13777,6 @@
         </is>
       </c>
       <c r="Q212" t="inlineStr"/>
-      <c r="R212" t="inlineStr"/>
-      <c r="S212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -14290,7 +13786,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>GM 282</t>
+          <t>Principles of Geographic Information Systems</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -14346,8 +13842,6 @@
         </is>
       </c>
       <c r="Q213" t="inlineStr"/>
-      <c r="R213" t="inlineStr"/>
-      <c r="S213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -14357,7 +13851,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>GM 350</t>
+          <t>Mineral Resource Estimation</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -14413,8 +13907,6 @@
         </is>
       </c>
       <c r="Q214" t="inlineStr"/>
-      <c r="R214" t="inlineStr"/>
-      <c r="S214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -14424,7 +13916,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>GM 352</t>
+          <t>Research Methods and Ethics</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -14480,8 +13972,6 @@
         </is>
       </c>
       <c r="Q215" t="inlineStr"/>
-      <c r="R215" t="inlineStr"/>
-      <c r="S215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -14491,7 +13981,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>GM 356</t>
+          <t>Fieldtrip &amp; Technical Report Writing II</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -14543,8 +14033,6 @@
       </c>
       <c r="P216" t="inlineStr"/>
       <c r="Q216" t="inlineStr"/>
-      <c r="R216" t="inlineStr"/>
-      <c r="S216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -14554,7 +14042,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>GM 370</t>
+          <t>Computer Applications in Geomatic Engineering *</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -14610,8 +14098,6 @@
         </is>
       </c>
       <c r="Q217" t="inlineStr"/>
-      <c r="R217" t="inlineStr"/>
-      <c r="S217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -14621,7 +14107,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>GM 372</t>
+          <t>Survey Computation &amp; Adjustment II</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -14677,8 +14163,6 @@
         </is>
       </c>
       <c r="Q218" t="inlineStr"/>
-      <c r="R218" t="inlineStr"/>
-      <c r="S218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -14688,7 +14172,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>GM 374</t>
+          <t>Hydrographic Surveying</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -14744,8 +14228,6 @@
         </is>
       </c>
       <c r="Q219" t="inlineStr"/>
-      <c r="R219" t="inlineStr"/>
-      <c r="S219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -14755,7 +14237,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>GM 376</t>
+          <t>Advanced Geodesy</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -14811,8 +14293,6 @@
         </is>
       </c>
       <c r="Q220" t="inlineStr"/>
-      <c r="R220" t="inlineStr"/>
-      <c r="S220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -14822,7 +14302,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>GM 380</t>
+          <t>Survey Camp II**</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -14874,8 +14354,6 @@
       </c>
       <c r="P221" t="inlineStr"/>
       <c r="Q221" t="inlineStr"/>
-      <c r="R221" t="inlineStr"/>
-      <c r="S221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -14885,7 +14363,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>GM 382</t>
+          <t>Application of Artificial Intelligence</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -14941,8 +14419,6 @@
         </is>
       </c>
       <c r="Q222" t="inlineStr"/>
-      <c r="R222" t="inlineStr"/>
-      <c r="S222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -15008,8 +14484,6 @@
         </is>
       </c>
       <c r="Q223" t="inlineStr"/>
-      <c r="R223" t="inlineStr"/>
-      <c r="S223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -15019,7 +14493,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>GM 456</t>
+          <t>Transportation &amp; Highway Engineering</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -15071,8 +14545,6 @@
       </c>
       <c r="P224" t="inlineStr"/>
       <c r="Q224" t="inlineStr"/>
-      <c r="R224" t="inlineStr"/>
-      <c r="S224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -15082,7 +14554,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>ES 458/GL 458/GM 458</t>
+          <t>Organisational Leadership and Management</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -15138,12 +14610,6 @@
         </is>
       </c>
       <c r="Q225" t="inlineStr"/>
-      <c r="R225" t="inlineStr">
-        <is>
-          <t>joint-422</t>
-        </is>
-      </c>
-      <c r="S225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -15153,7 +14619,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>ES 458/GL 458/GM 458</t>
+          <t>Organisational Leadership and Management</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -15209,12 +14675,6 @@
         </is>
       </c>
       <c r="Q226" t="inlineStr"/>
-      <c r="R226" t="inlineStr">
-        <is>
-          <t>joint-422</t>
-        </is>
-      </c>
-      <c r="S226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -15224,7 +14684,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>ES 466/GM 466</t>
+          <t>Law of Contract and Tort</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -15280,12 +14740,6 @@
         </is>
       </c>
       <c r="Q227" t="inlineStr"/>
-      <c r="R227" t="inlineStr">
-        <is>
-          <t>joint-423</t>
-        </is>
-      </c>
-      <c r="S227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -15295,7 +14749,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>ES 466/GM 466</t>
+          <t>Law of Contract and Tort</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -15351,12 +14805,6 @@
         </is>
       </c>
       <c r="Q228" t="inlineStr"/>
-      <c r="R228" t="inlineStr">
-        <is>
-          <t>joint-423</t>
-        </is>
-      </c>
-      <c r="S228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -15366,7 +14814,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>GM 472</t>
+          <t>Ghana Land Law</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -15422,8 +14870,6 @@
         </is>
       </c>
       <c r="Q229" t="inlineStr"/>
-      <c r="R229" t="inlineStr"/>
-      <c r="S229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -15485,8 +14931,6 @@
       </c>
       <c r="P230" t="inlineStr"/>
       <c r="Q230" t="inlineStr"/>
-      <c r="R230" t="inlineStr"/>
-      <c r="S230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -15496,7 +14940,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>MA 470</t>
+          <t>Designs and Analysis of Experiments</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -15552,8 +14996,6 @@
         </is>
       </c>
       <c r="Q231" t="inlineStr"/>
-      <c r="R231" t="inlineStr"/>
-      <c r="S231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -15563,7 +15005,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>MA 472</t>
+          <t>Mathematical Economics II</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -15615,8 +15057,6 @@
       </c>
       <c r="P232" t="inlineStr"/>
       <c r="Q232" t="inlineStr"/>
-      <c r="R232" t="inlineStr"/>
-      <c r="S232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -15626,7 +15066,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>MA 474</t>
+          <t>Time Series and Forecasting</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -15678,8 +15118,6 @@
       </c>
       <c r="P233" t="inlineStr"/>
       <c r="Q233" t="inlineStr"/>
-      <c r="R233" t="inlineStr"/>
-      <c r="S233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -15689,7 +15127,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>MC 142</t>
+          <t>Basic French   II</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -15745,8 +15183,6 @@
         </is>
       </c>
       <c r="Q234" t="inlineStr"/>
-      <c r="R234" t="inlineStr"/>
-      <c r="S234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -15756,7 +15192,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>MC 156</t>
+          <t>Engineering Drawing</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -15812,8 +15248,6 @@
         </is>
       </c>
       <c r="Q235" t="inlineStr"/>
-      <c r="R235" t="inlineStr"/>
-      <c r="S235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -15823,7 +15257,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>MC 158</t>
+          <t>Academic Writing</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -15879,8 +15313,6 @@
         </is>
       </c>
       <c r="Q236" t="inlineStr"/>
-      <c r="R236" t="inlineStr"/>
-      <c r="S236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -15890,7 +15322,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>MC 164/PM 134</t>
+          <t>Basic Electronics</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -15942,8 +15374,6 @@
         </is>
       </c>
       <c r="Q237" t="inlineStr"/>
-      <c r="R237" t="inlineStr"/>
-      <c r="S237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -15953,7 +15383,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>MC 164/PM 134</t>
+          <t>Basic Electronics</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -16001,8 +15431,6 @@
       </c>
       <c r="P238" t="inlineStr"/>
       <c r="Q238" t="inlineStr"/>
-      <c r="R238" t="inlineStr"/>
-      <c r="S238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -16012,7 +15440,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>MC 166</t>
+          <t>Calculus</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -16064,8 +15492,6 @@
       </c>
       <c r="P239" t="inlineStr"/>
       <c r="Q239" t="inlineStr"/>
-      <c r="R239" t="inlineStr"/>
-      <c r="S239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -16075,7 +15501,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>MC 168</t>
+          <t>Basic Material Science</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -16131,8 +15557,6 @@
         </is>
       </c>
       <c r="Q240" t="inlineStr"/>
-      <c r="R240" t="inlineStr"/>
-      <c r="S240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -16142,7 +15566,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>MC 170</t>
+          <t>Workshop Technology and Practice</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -16194,8 +15618,6 @@
       </c>
       <c r="P241" t="inlineStr"/>
       <c r="Q241" t="inlineStr"/>
-      <c r="R241" t="inlineStr"/>
-      <c r="S241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -16205,7 +15627,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>MC 172</t>
+          <t>Strength of Materials I</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -16257,8 +15679,6 @@
       </c>
       <c r="P242" t="inlineStr"/>
       <c r="Q242" t="inlineStr"/>
-      <c r="R242" t="inlineStr"/>
-      <c r="S242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -16268,7 +15688,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>MC 174</t>
+          <t>Mechanics II: Dynanics</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -16320,8 +15740,6 @@
       </c>
       <c r="P243" t="inlineStr"/>
       <c r="Q243" t="inlineStr"/>
-      <c r="R243" t="inlineStr"/>
-      <c r="S243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -16331,7 +15749,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>MC 252</t>
+          <t>Engineering Practice</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -16383,8 +15801,6 @@
       </c>
       <c r="P244" t="inlineStr"/>
       <c r="Q244" t="inlineStr"/>
-      <c r="R244" t="inlineStr"/>
-      <c r="S244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -16394,7 +15810,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>MC 256</t>
+          <t>Critical Thinking and Intergrated Thought</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -16450,8 +15866,6 @@
         </is>
       </c>
       <c r="Q245" t="inlineStr"/>
-      <c r="R245" t="inlineStr"/>
-      <c r="S245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -16461,7 +15875,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>MC 260</t>
+          <t>Mathematics Analysis</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -16517,8 +15931,6 @@
         </is>
       </c>
       <c r="Q246" t="inlineStr"/>
-      <c r="R246" t="inlineStr"/>
-      <c r="S246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -16528,7 +15940,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>MC 264</t>
+          <t>Fluid Mechanics</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -16584,8 +15996,6 @@
         </is>
       </c>
       <c r="Q247" t="inlineStr"/>
-      <c r="R247" t="inlineStr"/>
-      <c r="S247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -16595,7 +16005,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>MC 270</t>
+          <t>Applied Thermodynamics</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -16651,8 +16061,6 @@
         </is>
       </c>
       <c r="Q248" t="inlineStr"/>
-      <c r="R248" t="inlineStr"/>
-      <c r="S248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -16662,7 +16070,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>MC 272</t>
+          <t>Mechanics of Machines II</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -16718,8 +16126,6 @@
         </is>
       </c>
       <c r="Q249" t="inlineStr"/>
-      <c r="R249" t="inlineStr"/>
-      <c r="S249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -16729,7 +16135,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>MC 274</t>
+          <t>Machines Design I</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -16785,8 +16191,6 @@
         </is>
       </c>
       <c r="Q250" t="inlineStr"/>
-      <c r="R250" t="inlineStr"/>
-      <c r="S250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -16796,7 +16200,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>MC 276</t>
+          <t>Manufacturing Technology</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -16848,8 +16252,6 @@
       </c>
       <c r="P251" t="inlineStr"/>
       <c r="Q251" t="inlineStr"/>
-      <c r="R251" t="inlineStr"/>
-      <c r="S251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -16859,7 +16261,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>MC 352</t>
+          <t>Resaech Methods and Ethics</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -16911,8 +16313,6 @@
       </c>
       <c r="P252" t="inlineStr"/>
       <c r="Q252" t="inlineStr"/>
-      <c r="R252" t="inlineStr"/>
-      <c r="S252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -16922,7 +16322,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>EL 354/MC 354</t>
+          <t>Business Entrepreneurship</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -16978,12 +16378,6 @@
         </is>
       </c>
       <c r="Q253" t="inlineStr"/>
-      <c r="R253" t="inlineStr">
-        <is>
-          <t>joint-477</t>
-        </is>
-      </c>
-      <c r="S253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -16993,7 +16387,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>EL 354/MC 354</t>
+          <t>Business Entreprenureship</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -17049,12 +16443,6 @@
         </is>
       </c>
       <c r="Q254" t="inlineStr"/>
-      <c r="R254" t="inlineStr">
-        <is>
-          <t>joint-477</t>
-        </is>
-      </c>
-      <c r="S254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -17064,7 +16452,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>MC 358</t>
+          <t>Heat Transfer</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -17116,8 +16504,6 @@
       </c>
       <c r="P255" t="inlineStr"/>
       <c r="Q255" t="inlineStr"/>
-      <c r="R255" t="inlineStr"/>
-      <c r="S255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -17127,7 +16513,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>MC 364</t>
+          <t>Data Science and  Machine Learning  Fundamentals</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -17179,8 +16565,6 @@
       </c>
       <c r="P256" t="inlineStr"/>
       <c r="Q256" t="inlineStr"/>
-      <c r="R256" t="inlineStr"/>
-      <c r="S256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -17190,7 +16574,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>MC 374</t>
+          <t>Machine Design III</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -17242,8 +16626,6 @@
       </c>
       <c r="P257" t="inlineStr"/>
       <c r="Q257" t="inlineStr"/>
-      <c r="R257" t="inlineStr"/>
-      <c r="S257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -17253,7 +16635,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>MC 376</t>
+          <t>Electrical Machines</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -17305,8 +16687,6 @@
       </c>
       <c r="P258" t="inlineStr"/>
       <c r="Q258" t="inlineStr"/>
-      <c r="R258" t="inlineStr"/>
-      <c r="S258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -17372,8 +16752,6 @@
         </is>
       </c>
       <c r="Q259" t="inlineStr"/>
-      <c r="R259" t="inlineStr"/>
-      <c r="S259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -17383,7 +16761,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>CE 458/EL 458/MA 458/MC 458</t>
+          <t>Organisational Leadership and Management</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -17439,12 +16817,6 @@
         </is>
       </c>
       <c r="Q260" t="inlineStr"/>
-      <c r="R260" t="inlineStr">
-        <is>
-          <t>joint-490</t>
-        </is>
-      </c>
-      <c r="S260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -17454,7 +16826,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>CE 458/EL 458/MA 458/MC 458</t>
+          <t>Organisational Leadership and Management</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -17510,12 +16882,6 @@
         </is>
       </c>
       <c r="Q261" t="inlineStr"/>
-      <c r="R261" t="inlineStr">
-        <is>
-          <t>joint-490</t>
-        </is>
-      </c>
-      <c r="S261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -17525,7 +16891,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>MA 460/MC 460</t>
+          <t>Corporate Social Responsibility</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -17581,12 +16947,6 @@
         </is>
       </c>
       <c r="Q262" t="inlineStr"/>
-      <c r="R262" t="inlineStr">
-        <is>
-          <t>joint-491</t>
-        </is>
-      </c>
-      <c r="S262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -17596,7 +16956,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>MA 460/MC 460</t>
+          <t>Corporate Social Responsibility</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -17652,12 +17012,6 @@
         </is>
       </c>
       <c r="Q263" t="inlineStr"/>
-      <c r="R263" t="inlineStr">
-        <is>
-          <t>joint-491</t>
-        </is>
-      </c>
-      <c r="S263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -17667,7 +17021,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>EL 462/MC 462</t>
+          <t>Industrial &amp; Maintenance  Engineering</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -17723,12 +17077,6 @@
         </is>
       </c>
       <c r="Q264" t="inlineStr"/>
-      <c r="R264" t="inlineStr">
-        <is>
-          <t>joint-492</t>
-        </is>
-      </c>
-      <c r="S264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -17738,7 +17086,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>EL 462/MC 462</t>
+          <t>Industrial &amp; Maintenance  Engineering</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -17794,12 +17142,6 @@
         </is>
       </c>
       <c r="Q265" t="inlineStr"/>
-      <c r="R265" t="inlineStr">
-        <is>
-          <t>joint-492</t>
-        </is>
-      </c>
-      <c r="S265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -17809,7 +17151,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>EL 466/MA 466/MC 466</t>
+          <t>Law of Contract and Tort</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -17865,12 +17207,6 @@
         </is>
       </c>
       <c r="Q266" t="inlineStr"/>
-      <c r="R266" t="inlineStr">
-        <is>
-          <t>joint-493</t>
-        </is>
-      </c>
-      <c r="S266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -17880,7 +17216,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>EL 466/MA 466/MC 466</t>
+          <t>Law of Contract and Tort</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -17936,12 +17272,6 @@
         </is>
       </c>
       <c r="Q267" t="inlineStr"/>
-      <c r="R267" t="inlineStr">
-        <is>
-          <t>joint-493</t>
-        </is>
-      </c>
-      <c r="S267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -17951,7 +17281,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>EL 466/MA 466/MC 466</t>
+          <t>Law of Contract and Tort</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -18007,12 +17337,6 @@
         </is>
       </c>
       <c r="Q268" t="inlineStr"/>
-      <c r="R268" t="inlineStr">
-        <is>
-          <t>joint-493</t>
-        </is>
-      </c>
-      <c r="S268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -18022,7 +17346,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>MC 470</t>
+          <t>Introduction to Automobile Engineering</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -18074,8 +17398,6 @@
       </c>
       <c r="P269" t="inlineStr"/>
       <c r="Q269" t="inlineStr"/>
-      <c r="R269" t="inlineStr"/>
-      <c r="S269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -18085,7 +17407,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>MC 472</t>
+          <t>Turbomachinery</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -18141,8 +17463,6 @@
         </is>
       </c>
       <c r="Q270" t="inlineStr"/>
-      <c r="R270" t="inlineStr"/>
-      <c r="S270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -18152,7 +17472,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>MF 170</t>
+          <t>Discrete Mathematics and Theory of Proofs</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -18204,8 +17524,6 @@
       </c>
       <c r="P271" t="inlineStr"/>
       <c r="Q271" t="inlineStr"/>
-      <c r="R271" t="inlineStr"/>
-      <c r="S271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -18215,7 +17533,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>MF 172</t>
+          <t>Calculus</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -18267,8 +17585,6 @@
       </c>
       <c r="P272" t="inlineStr"/>
       <c r="Q272" t="inlineStr"/>
-      <c r="R272" t="inlineStr"/>
-      <c r="S272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -18278,7 +17594,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>MF 174</t>
+          <t>Statistical Methods</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -18330,8 +17646,6 @@
       </c>
       <c r="P273" t="inlineStr"/>
       <c r="Q273" t="inlineStr"/>
-      <c r="R273" t="inlineStr"/>
-      <c r="S273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -18341,7 +17655,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>MF 176</t>
+          <t>Financial Mathematics</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -18393,8 +17707,6 @@
       </c>
       <c r="P274" t="inlineStr"/>
       <c r="Q274" t="inlineStr"/>
-      <c r="R274" t="inlineStr"/>
-      <c r="S274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -18404,7 +17716,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>MF 178</t>
+          <t>Principles of Macroeconomics</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -18460,8 +17772,6 @@
         </is>
       </c>
       <c r="Q275" t="inlineStr"/>
-      <c r="R275" t="inlineStr"/>
-      <c r="S275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -18471,7 +17781,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>PM 132</t>
+          <t>Thermodynamics</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -18523,8 +17833,6 @@
       </c>
       <c r="P276" t="inlineStr"/>
       <c r="Q276" t="inlineStr"/>
-      <c r="R276" t="inlineStr"/>
-      <c r="S276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -18534,7 +17842,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>PM 136</t>
+          <t>Engineering Drawing with AutoCAD</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -18586,8 +17894,6 @@
       </c>
       <c r="P277" t="inlineStr"/>
       <c r="Q277" t="inlineStr"/>
-      <c r="R277" t="inlineStr"/>
-      <c r="S277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -18597,7 +17903,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>PM 140</t>
+          <t>Strength of Materials</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -18649,8 +17955,6 @@
       </c>
       <c r="P278" t="inlineStr"/>
       <c r="Q278" t="inlineStr"/>
-      <c r="R278" t="inlineStr"/>
-      <c r="S278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -18660,7 +17964,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>PM 142</t>
+          <t>Dynamics of Solid Mechanics</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -18712,8 +18016,6 @@
       </c>
       <c r="P279" t="inlineStr"/>
       <c r="Q279" t="inlineStr"/>
-      <c r="R279" t="inlineStr"/>
-      <c r="S279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -18723,7 +18025,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>PM 144</t>
+          <t>Calculus</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -18775,8 +18077,6 @@
       </c>
       <c r="P280" t="inlineStr"/>
       <c r="Q280" t="inlineStr"/>
-      <c r="R280" t="inlineStr"/>
-      <c r="S280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -18786,7 +18086,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>PM 146</t>
+          <t>Metrology</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -18838,8 +18138,6 @@
       </c>
       <c r="P281" t="inlineStr"/>
       <c r="Q281" t="inlineStr"/>
-      <c r="R281" t="inlineStr"/>
-      <c r="S281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -18849,7 +18147,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>DS 142/MF 142/TM 142</t>
+          <t>Basic French II</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -18901,14 +18199,6 @@
       </c>
       <c r="P282" t="inlineStr"/>
       <c r="Q282" t="inlineStr"/>
-      <c r="R282" t="inlineStr">
-        <is>
-          <t>joint-516</t>
-        </is>
-      </c>
-      <c r="S282" t="n">
-        <v>80</v>
-      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -18918,7 +18208,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>DS 142/MF 142/TM 142</t>
+          <t>Basic French II</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -18970,14 +18260,6 @@
       </c>
       <c r="P283" t="inlineStr"/>
       <c r="Q283" t="inlineStr"/>
-      <c r="R283" t="inlineStr">
-        <is>
-          <t>joint-516</t>
-        </is>
-      </c>
-      <c r="S283" t="n">
-        <v>80</v>
-      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -18987,7 +18269,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>DS 142/MF 142/TM 142</t>
+          <t>Basic French II</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -19039,14 +18321,6 @@
       </c>
       <c r="P284" t="inlineStr"/>
       <c r="Q284" t="inlineStr"/>
-      <c r="R284" t="inlineStr">
-        <is>
-          <t>joint-516</t>
-        </is>
-      </c>
-      <c r="S284" t="n">
-        <v>80</v>
-      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -19056,7 +18330,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>TM 144</t>
+          <t>Introduction to Railway Engineering</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -19108,8 +18382,6 @@
       </c>
       <c r="P285" t="inlineStr"/>
       <c r="Q285" t="inlineStr"/>
-      <c r="R285" t="inlineStr"/>
-      <c r="S285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -19119,7 +18391,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>TM 156</t>
+          <t>Organisational Behaviour</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -19175,8 +18447,6 @@
         </is>
       </c>
       <c r="Q286" t="inlineStr"/>
-      <c r="R286" t="inlineStr"/>
-      <c r="S286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -19186,7 +18456,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>TM 164</t>
+          <t>Quantitative Methods II</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -19238,8 +18508,6 @@
       </c>
       <c r="P287" t="inlineStr"/>
       <c r="Q287" t="inlineStr"/>
-      <c r="R287" t="inlineStr"/>
-      <c r="S287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -19249,7 +18517,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>TM 170</t>
+          <t>Occupational Health and Safety</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -19301,8 +18569,6 @@
       </c>
       <c r="P288" t="inlineStr"/>
       <c r="Q288" t="inlineStr"/>
-      <c r="R288" t="inlineStr"/>
-      <c r="S288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -19312,7 +18578,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>TM 172</t>
+          <t>Principles of Management</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -19364,8 +18630,6 @@
       </c>
       <c r="P289" t="inlineStr"/>
       <c r="Q289" t="inlineStr"/>
-      <c r="R289" t="inlineStr"/>
-      <c r="S289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -19375,7 +18639,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>TM 174</t>
+          <t>Public Transport</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -19427,8 +18691,6 @@
       </c>
       <c r="P290" t="inlineStr"/>
       <c r="Q290" t="inlineStr"/>
-      <c r="R290" t="inlineStr"/>
-      <c r="S290" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/semesters/sem2/courses.xlsx
+++ b/data/semesters/sem2/courses.xlsx
@@ -1804,11 +1804,7 @@
       <c r="Q21" t="n">
         <v>119</v>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>joint-20</t>
-        </is>
-      </c>
+      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1873,11 +1869,7 @@
       <c r="Q22" t="n">
         <v>15</v>
       </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>joint-20</t>
-        </is>
-      </c>
+      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -4719,11 +4711,7 @@
       <c r="Q66" t="n">
         <v>119</v>
       </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>joint-64</t>
-        </is>
-      </c>
+      <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
     </row>
     <row r="67">
@@ -4792,11 +4780,7 @@
       <c r="Q67" t="n">
         <v>116</v>
       </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>joint-64</t>
-        </is>
-      </c>
+      <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
     </row>
     <row r="68">
@@ -12121,11 +12105,7 @@
       <c r="Q180" t="n">
         <v>120</v>
       </c>
-      <c r="R180" t="inlineStr">
-        <is>
-          <t>joint-175</t>
-        </is>
-      </c>
+      <c r="R180" t="inlineStr"/>
       <c r="S180" t="inlineStr"/>
     </row>
     <row r="181">
@@ -12194,11 +12174,7 @@
       <c r="Q181" t="n">
         <v>25</v>
       </c>
-      <c r="R181" t="inlineStr">
-        <is>
-          <t>joint-175</t>
-        </is>
-      </c>
+      <c r="R181" t="inlineStr"/>
       <c r="S181" t="inlineStr"/>
     </row>
     <row r="182">
@@ -18392,11 +18368,7 @@
       <c r="Q277" t="n">
         <v>112</v>
       </c>
-      <c r="R277" t="inlineStr">
-        <is>
-          <t>joint-271</t>
-        </is>
-      </c>
+      <c r="R277" t="inlineStr"/>
       <c r="S277" t="inlineStr"/>
     </row>
     <row r="278">
@@ -18465,11 +18437,7 @@
       <c r="Q278" t="n">
         <v>116</v>
       </c>
-      <c r="R278" t="inlineStr">
-        <is>
-          <t>joint-271</t>
-        </is>
-      </c>
+      <c r="R278" t="inlineStr"/>
       <c r="S278" t="inlineStr"/>
     </row>
     <row r="279">
@@ -19562,11 +19530,7 @@
       <c r="Q295" t="n">
         <v>112</v>
       </c>
-      <c r="R295" t="inlineStr">
-        <is>
-          <t>joint-288</t>
-        </is>
-      </c>
+      <c r="R295" t="inlineStr"/>
       <c r="S295" t="inlineStr"/>
     </row>
     <row r="296">
@@ -19635,11 +19599,7 @@
       <c r="Q296" t="n">
         <v>112</v>
       </c>
-      <c r="R296" t="inlineStr">
-        <is>
-          <t>joint-288</t>
-        </is>
-      </c>
+      <c r="R296" t="inlineStr"/>
       <c r="S296" t="inlineStr"/>
     </row>
     <row r="297">
@@ -19708,11 +19668,7 @@
       <c r="Q297" t="n">
         <v>116</v>
       </c>
-      <c r="R297" t="inlineStr">
-        <is>
-          <t>joint-288</t>
-        </is>
-      </c>
+      <c r="R297" t="inlineStr"/>
       <c r="S297" t="inlineStr"/>
     </row>
     <row r="298">
@@ -24094,11 +24050,7 @@
       <c r="Q365" t="n">
         <v>112</v>
       </c>
-      <c r="R365" t="inlineStr">
-        <is>
-          <t>joint-356</t>
-        </is>
-      </c>
+      <c r="R365" t="inlineStr"/>
       <c r="S365" t="inlineStr"/>
     </row>
     <row r="366">
@@ -24167,11 +24119,7 @@
       <c r="Q366" t="n">
         <v>119</v>
       </c>
-      <c r="R366" t="inlineStr">
-        <is>
-          <t>joint-356</t>
-        </is>
-      </c>
+      <c r="R366" t="inlineStr"/>
       <c r="S366" t="inlineStr"/>
     </row>
     <row r="367">
@@ -26696,11 +26644,7 @@
       <c r="Q405" t="n">
         <v>116</v>
       </c>
-      <c r="R405" t="inlineStr">
-        <is>
-          <t>joint-395</t>
-        </is>
-      </c>
+      <c r="R405" t="inlineStr"/>
       <c r="S405" t="inlineStr"/>
     </row>
     <row r="406">
@@ -26769,11 +26713,7 @@
       <c r="Q406" t="n">
         <v>116</v>
       </c>
-      <c r="R406" t="inlineStr">
-        <is>
-          <t>joint-395</t>
-        </is>
-      </c>
+      <c r="R406" t="inlineStr"/>
       <c r="S406" t="inlineStr"/>
     </row>
     <row r="407">
@@ -26842,11 +26782,7 @@
       <c r="Q407" t="n">
         <v>112</v>
       </c>
-      <c r="R407" t="inlineStr">
-        <is>
-          <t>joint-395</t>
-        </is>
-      </c>
+      <c r="R407" t="inlineStr"/>
       <c r="S407" t="inlineStr"/>
     </row>
     <row r="408">
@@ -28579,11 +28515,7 @@
       <c r="Q434" t="n">
         <v>116</v>
       </c>
-      <c r="R434" t="inlineStr">
-        <is>
-          <t>joint-422</t>
-        </is>
-      </c>
+      <c r="R434" t="inlineStr"/>
       <c r="S434" t="inlineStr"/>
     </row>
     <row r="435">
@@ -28652,11 +28584,7 @@
       <c r="Q435" t="n">
         <v>112</v>
       </c>
-      <c r="R435" t="inlineStr">
-        <is>
-          <t>joint-422</t>
-        </is>
-      </c>
+      <c r="R435" t="inlineStr"/>
       <c r="S435" t="inlineStr"/>
     </row>
     <row r="436">
@@ -28725,11 +28653,7 @@
       <c r="Q436" t="n">
         <v>112</v>
       </c>
-      <c r="R436" t="inlineStr">
-        <is>
-          <t>joint-422</t>
-        </is>
-      </c>
+      <c r="R436" t="inlineStr"/>
       <c r="S436" t="inlineStr"/>
     </row>
     <row r="437">
@@ -28798,11 +28722,7 @@
       <c r="Q437" t="n">
         <v>116</v>
       </c>
-      <c r="R437" t="inlineStr">
-        <is>
-          <t>joint-423</t>
-        </is>
-      </c>
+      <c r="R437" t="inlineStr"/>
       <c r="S437" t="inlineStr"/>
     </row>
     <row r="438">
@@ -28871,11 +28791,7 @@
       <c r="Q438" t="n">
         <v>112</v>
       </c>
-      <c r="R438" t="inlineStr">
-        <is>
-          <t>joint-423</t>
-        </is>
-      </c>
+      <c r="R438" t="inlineStr"/>
       <c r="S438" t="inlineStr"/>
     </row>
     <row r="439">
@@ -29858,14 +29774,8 @@
       <c r="Q453" t="n">
         <v>117</v>
       </c>
-      <c r="R453" t="inlineStr">
-        <is>
-          <t>joint-437</t>
-        </is>
-      </c>
-      <c r="S453" t="n">
-        <v>120</v>
-      </c>
+      <c r="R453" t="inlineStr"/>
+      <c r="S453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -29929,14 +29839,8 @@
       <c r="Q454" t="n">
         <v>15</v>
       </c>
-      <c r="R454" t="inlineStr">
-        <is>
-          <t>joint-437</t>
-        </is>
-      </c>
-      <c r="S454" t="n">
-        <v>120</v>
-      </c>
+      <c r="R454" t="inlineStr"/>
+      <c r="S454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -33181,11 +33085,7 @@
       <c r="Q504" t="n">
         <v>117</v>
       </c>
-      <c r="R504" t="inlineStr">
-        <is>
-          <t>joint-487</t>
-        </is>
-      </c>
+      <c r="R504" t="inlineStr"/>
       <c r="S504" t="inlineStr"/>
     </row>
     <row r="505">
@@ -33254,11 +33154,7 @@
       <c r="Q505" t="n">
         <v>120</v>
       </c>
-      <c r="R505" t="inlineStr">
-        <is>
-          <t>joint-487</t>
-        </is>
-      </c>
+      <c r="R505" t="inlineStr"/>
       <c r="S505" t="inlineStr"/>
     </row>
     <row r="506">
@@ -33969,11 +33865,7 @@
       <c r="Q516" t="n">
         <v>117</v>
       </c>
-      <c r="R516" t="inlineStr">
-        <is>
-          <t>joint-498</t>
-        </is>
-      </c>
+      <c r="R516" t="inlineStr"/>
       <c r="S516" t="inlineStr"/>
     </row>
     <row r="517">
@@ -34042,11 +33934,7 @@
       <c r="Q517" t="n">
         <v>119</v>
       </c>
-      <c r="R517" t="inlineStr">
-        <is>
-          <t>joint-498</t>
-        </is>
-      </c>
+      <c r="R517" t="inlineStr"/>
       <c r="S517" t="inlineStr"/>
     </row>
     <row r="518">
@@ -34115,11 +34003,7 @@
       <c r="Q518" t="n">
         <v>120</v>
       </c>
-      <c r="R518" t="inlineStr">
-        <is>
-          <t>joint-498</t>
-        </is>
-      </c>
+      <c r="R518" t="inlineStr"/>
       <c r="S518" t="inlineStr"/>
     </row>
     <row r="519">
@@ -34188,11 +34072,7 @@
       <c r="Q519" t="n">
         <v>40</v>
       </c>
-      <c r="R519" t="inlineStr">
-        <is>
-          <t>joint-498</t>
-        </is>
-      </c>
+      <c r="R519" t="inlineStr"/>
       <c r="S519" t="inlineStr"/>
     </row>
     <row r="520">
@@ -34261,11 +34141,7 @@
       <c r="Q520" t="n">
         <v>117</v>
       </c>
-      <c r="R520" t="inlineStr">
-        <is>
-          <t>joint-499</t>
-        </is>
-      </c>
+      <c r="R520" t="inlineStr"/>
       <c r="S520" t="inlineStr"/>
     </row>
     <row r="521">
@@ -34334,11 +34210,7 @@
       <c r="Q521" t="n">
         <v>40</v>
       </c>
-      <c r="R521" t="inlineStr">
-        <is>
-          <t>joint-499</t>
-        </is>
-      </c>
+      <c r="R521" t="inlineStr"/>
       <c r="S521" t="inlineStr"/>
     </row>
     <row r="522">
@@ -34407,11 +34279,7 @@
       <c r="Q522" t="n">
         <v>117</v>
       </c>
-      <c r="R522" t="inlineStr">
-        <is>
-          <t>joint-500</t>
-        </is>
-      </c>
+      <c r="R522" t="inlineStr"/>
       <c r="S522" t="inlineStr"/>
     </row>
     <row r="523">
@@ -34480,11 +34348,7 @@
       <c r="Q523" t="n">
         <v>120</v>
       </c>
-      <c r="R523" t="inlineStr">
-        <is>
-          <t>joint-500</t>
-        </is>
-      </c>
+      <c r="R523" t="inlineStr"/>
       <c r="S523" t="inlineStr"/>
     </row>
     <row r="524">
@@ -34553,11 +34417,7 @@
       <c r="Q524" t="n">
         <v>117</v>
       </c>
-      <c r="R524" t="inlineStr">
-        <is>
-          <t>joint-501</t>
-        </is>
-      </c>
+      <c r="R524" t="inlineStr"/>
       <c r="S524" t="inlineStr"/>
     </row>
     <row r="525">
@@ -34626,11 +34486,7 @@
       <c r="Q525" t="n">
         <v>120</v>
       </c>
-      <c r="R525" t="inlineStr">
-        <is>
-          <t>joint-501</t>
-        </is>
-      </c>
+      <c r="R525" t="inlineStr"/>
       <c r="S525" t="inlineStr"/>
     </row>
     <row r="526">
@@ -34699,11 +34555,7 @@
       <c r="Q526" t="n">
         <v>40</v>
       </c>
-      <c r="R526" t="inlineStr">
-        <is>
-          <t>joint-501</t>
-        </is>
-      </c>
+      <c r="R526" t="inlineStr"/>
       <c r="S526" t="inlineStr"/>
     </row>
     <row r="527">
